--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46A46074-F941-47B7-9E90-35B5D4FDAEEE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6216CF9-3C3D-4669-A399-0383EDCA269A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -657,23 +657,34 @@
       <c r="D6" s="1">
         <v>45</v>
       </c>
-      <c r="E6" s="1"/>
+      <c r="E6" s="1">
+        <f>66.5+16</f>
+        <v>82.5</v>
+      </c>
       <c r="F6" s="1">
         <v>35.1</v>
       </c>
-      <c r="G6" s="1"/>
+      <c r="G6" s="1">
+        <v>55.5</v>
+      </c>
       <c r="H6" s="1">
         <v>30</v>
       </c>
-      <c r="I6" s="1"/>
+      <c r="I6" s="1">
+        <v>58.2</v>
+      </c>
       <c r="J6" s="1">
         <v>12</v>
       </c>
-      <c r="K6" s="1"/>
+      <c r="K6" s="1">
+        <v>9.1</v>
+      </c>
       <c r="L6" s="1">
         <v>13.5</v>
       </c>
-      <c r="M6" s="1"/>
+      <c r="M6" s="1">
+        <v>20.100000000000001</v>
+      </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
@@ -1751,23 +1762,34 @@
       <c r="D42" s="1">
         <v>15</v>
       </c>
-      <c r="E42" s="1"/>
+      <c r="E42" s="1">
+        <f>22.9+17</f>
+        <v>39.9</v>
+      </c>
       <c r="F42" s="1">
         <v>10</v>
       </c>
-      <c r="G42" s="1"/>
+      <c r="G42" s="1">
+        <v>11.4</v>
+      </c>
       <c r="H42" s="1">
         <v>7.4</v>
       </c>
-      <c r="I42" s="1"/>
+      <c r="I42" s="1">
+        <v>14.1</v>
+      </c>
       <c r="J42" s="1">
         <v>8</v>
       </c>
-      <c r="K42" s="1"/>
+      <c r="K42" s="1">
+        <v>7.7</v>
+      </c>
       <c r="L42" s="1">
         <v>2.8</v>
       </c>
-      <c r="M42" s="1"/>
+      <c r="M42" s="1">
+        <v>7.2</v>
+      </c>
     </row>
     <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="1">
@@ -2845,23 +2867,34 @@
       <c r="D77" s="1">
         <v>22</v>
       </c>
-      <c r="E77" s="1"/>
+      <c r="E77" s="1">
+        <f>27.5+2</f>
+        <v>29.5</v>
+      </c>
       <c r="F77" s="1">
         <v>6</v>
       </c>
-      <c r="G77" s="1"/>
+      <c r="G77" s="1">
+        <v>11.9</v>
+      </c>
       <c r="H77" s="1">
         <v>4.5</v>
       </c>
-      <c r="I77" s="1"/>
+      <c r="I77" s="1">
+        <v>10.5</v>
+      </c>
       <c r="J77" s="1">
         <v>5</v>
       </c>
-      <c r="K77" s="1"/>
+      <c r="K77" s="1">
+        <v>6.6</v>
+      </c>
       <c r="L77" s="1">
         <v>2.7</v>
       </c>
-      <c r="M77" s="1"/>
+      <c r="M77" s="1">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="78" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A78" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6216CF9-3C3D-4669-A399-0383EDCA269A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5632349-1883-4F83-A291-B29F5953C800}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -700,23 +700,34 @@
       <c r="D7" s="1">
         <v>45</v>
       </c>
-      <c r="E7" s="1"/>
+      <c r="E7" s="1">
+        <f>57.4+13</f>
+        <v>70.400000000000006</v>
+      </c>
       <c r="F7" s="1">
         <v>35.1</v>
       </c>
-      <c r="G7" s="1"/>
+      <c r="G7" s="1">
+        <v>47.7</v>
+      </c>
       <c r="H7" s="1">
         <v>30</v>
       </c>
-      <c r="I7" s="1"/>
+      <c r="I7" s="1">
+        <v>52.1</v>
+      </c>
       <c r="J7" s="1">
         <v>12</v>
       </c>
-      <c r="K7" s="1"/>
+      <c r="K7" s="1">
+        <v>12.6</v>
+      </c>
       <c r="L7" s="1">
         <v>13.5</v>
       </c>
-      <c r="M7" s="1"/>
+      <c r="M7" s="1">
+        <v>16.399999999999999</v>
+      </c>
     </row>
     <row r="8" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A8" s="2">
@@ -1583,21 +1594,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1641,13 +1652,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1672,9 +1683,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -1805,23 +1816,34 @@
       <c r="D43" s="1">
         <v>15</v>
       </c>
-      <c r="E43" s="1"/>
+      <c r="E43" s="1">
+        <f>15.5+17</f>
+        <v>32.5</v>
+      </c>
       <c r="F43" s="1">
         <v>10</v>
       </c>
-      <c r="G43" s="1"/>
+      <c r="G43" s="1">
+        <v>9.9</v>
+      </c>
       <c r="H43" s="1">
         <v>7.4</v>
       </c>
-      <c r="I43" s="1"/>
+      <c r="I43" s="1">
+        <v>12.7</v>
+      </c>
       <c r="J43" s="1">
         <v>8</v>
       </c>
-      <c r="K43" s="1"/>
+      <c r="K43" s="1">
+        <v>6.6</v>
+      </c>
       <c r="L43" s="1">
         <v>2.8</v>
       </c>
-      <c r="M43" s="1"/>
+      <c r="M43" s="1">
+        <v>6.4</v>
+      </c>
     </row>
     <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="2">
@@ -2688,21 +2710,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -2746,13 +2768,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2777,9 +2799,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -2910,23 +2932,34 @@
       <c r="D78" s="1">
         <v>22</v>
       </c>
-      <c r="E78" s="1"/>
+      <c r="E78" s="1">
+        <f>22.3+18</f>
+        <v>40.299999999999997</v>
+      </c>
       <c r="F78" s="1">
         <v>6</v>
       </c>
-      <c r="G78" s="1"/>
+      <c r="G78" s="1">
+        <v>9.6999999999999993</v>
+      </c>
       <c r="H78" s="1">
         <v>4.5</v>
       </c>
-      <c r="I78" s="1"/>
+      <c r="I78" s="1">
+        <v>14.3</v>
+      </c>
       <c r="J78" s="1">
         <v>5</v>
       </c>
-      <c r="K78" s="1"/>
+      <c r="K78" s="1">
+        <v>5.2</v>
+      </c>
       <c r="L78" s="1">
         <v>2.7</v>
       </c>
-      <c r="M78" s="1"/>
+      <c r="M78" s="1">
+        <v>7.8</v>
+      </c>
     </row>
     <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="2">
@@ -3794,6 +3827,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -3803,24 +3854,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5632349-1883-4F83-A291-B29F5953C800}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10AE540-1EBD-4ACC-B284-B5A591BAC8F0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -743,23 +743,34 @@
       <c r="D8" s="1">
         <v>45</v>
       </c>
-      <c r="E8" s="1"/>
+      <c r="E8" s="1">
+        <f>58.4</f>
+        <v>58.4</v>
+      </c>
       <c r="F8" s="1">
         <v>35.1</v>
       </c>
-      <c r="G8" s="1"/>
+      <c r="G8" s="1">
+        <v>55.4</v>
+      </c>
       <c r="H8" s="1">
         <v>30</v>
       </c>
-      <c r="I8" s="1"/>
+      <c r="I8" s="1">
+        <v>43</v>
+      </c>
       <c r="J8" s="1">
         <v>12</v>
       </c>
-      <c r="K8" s="1"/>
+      <c r="K8" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="L8" s="1">
         <v>13.5</v>
       </c>
-      <c r="M8" s="1"/>
+      <c r="M8" s="1">
+        <v>12.7</v>
+      </c>
     </row>
     <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
@@ -1594,21 +1605,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1652,13 +1663,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1683,9 +1694,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -1859,23 +1870,34 @@
       <c r="D44" s="1">
         <v>15</v>
       </c>
-      <c r="E44" s="1"/>
+      <c r="E44" s="1">
+        <f>24.8+15</f>
+        <v>39.799999999999997</v>
+      </c>
       <c r="F44" s="1">
         <v>10</v>
       </c>
-      <c r="G44" s="1"/>
+      <c r="G44" s="1">
+        <v>8.6</v>
+      </c>
       <c r="H44" s="1">
         <v>7.4</v>
       </c>
-      <c r="I44" s="1"/>
+      <c r="I44" s="1">
+        <v>10.9</v>
+      </c>
       <c r="J44" s="1">
         <v>8</v>
       </c>
-      <c r="K44" s="1"/>
+      <c r="K44" s="1">
+        <v>5.8</v>
+      </c>
       <c r="L44" s="1">
         <v>2.8</v>
       </c>
-      <c r="M44" s="1"/>
+      <c r="M44" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="1">
@@ -2710,21 +2732,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -2768,13 +2790,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2799,9 +2821,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -2975,23 +2997,34 @@
       <c r="D79" s="1">
         <v>22</v>
       </c>
-      <c r="E79" s="1"/>
+      <c r="E79" s="1">
+        <f>44.1</f>
+        <v>44.1</v>
+      </c>
       <c r="F79" s="1">
         <v>6</v>
       </c>
-      <c r="G79" s="1"/>
+      <c r="G79" s="1">
+        <v>11.5</v>
+      </c>
       <c r="H79" s="1">
         <v>4.5</v>
       </c>
-      <c r="I79" s="1"/>
+      <c r="I79" s="1">
+        <v>12.3</v>
+      </c>
       <c r="J79" s="1">
         <v>5</v>
       </c>
-      <c r="K79" s="1"/>
+      <c r="K79" s="1">
+        <v>9.6</v>
+      </c>
       <c r="L79" s="1">
         <v>2.7</v>
       </c>
-      <c r="M79" s="1"/>
+      <c r="M79" s="1">
+        <v>7.5</v>
+      </c>
     </row>
     <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1">
@@ -3827,6 +3860,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -3836,24 +3887,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="C74:C75"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -1,30 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10AE540-1EBD-4ACC-B284-B5A591BAC8F0}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD101A7-2B15-4C28-81E9-35F0E40EA325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029" refMode="R1C1"/>
+  <calcPr calcId="191029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
-    </ext>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -179,11 +173,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +472,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +530,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +561,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1605,21 +1599,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1663,13 +1657,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1694,9 +1688,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -1758,7 +1752,7 @@
         <v>16.100000000000001</v>
       </c>
       <c r="J41" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K41" s="1">
         <v>10.1</v>
@@ -1801,7 +1795,7 @@
         <v>14.1</v>
       </c>
       <c r="J42" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K42" s="1">
         <v>7.7</v>
@@ -1844,7 +1838,7 @@
         <v>12.7</v>
       </c>
       <c r="J43" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K43" s="1">
         <v>6.6</v>
@@ -1887,7 +1881,7 @@
         <v>10.9</v>
       </c>
       <c r="J44" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K44" s="1">
         <v>5.8</v>
@@ -1923,7 +1917,7 @@
       </c>
       <c r="I45" s="1"/>
       <c r="J45" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K45" s="1"/>
       <c r="L45" s="1">
@@ -1955,7 +1949,7 @@
       </c>
       <c r="I46" s="1"/>
       <c r="J46" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K46" s="1"/>
       <c r="L46" s="1">
@@ -1987,7 +1981,7 @@
       </c>
       <c r="I47" s="1"/>
       <c r="J47" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K47" s="1"/>
       <c r="L47" s="1">
@@ -2019,7 +2013,7 @@
       </c>
       <c r="I48" s="1"/>
       <c r="J48" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K48" s="1"/>
       <c r="L48" s="1">
@@ -2051,7 +2045,7 @@
       </c>
       <c r="I49" s="1"/>
       <c r="J49" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K49" s="1"/>
       <c r="L49" s="1">
@@ -2083,7 +2077,7 @@
       </c>
       <c r="I50" s="1"/>
       <c r="J50" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K50" s="1"/>
       <c r="L50" s="1">
@@ -2115,7 +2109,7 @@
       </c>
       <c r="I51" s="1"/>
       <c r="J51" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K51" s="1"/>
       <c r="L51" s="1">
@@ -2147,7 +2141,7 @@
       </c>
       <c r="I52" s="1"/>
       <c r="J52" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K52" s="1"/>
       <c r="L52" s="1">
@@ -2179,7 +2173,7 @@
       </c>
       <c r="I53" s="1"/>
       <c r="J53" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K53" s="1"/>
       <c r="L53" s="1">
@@ -2211,7 +2205,7 @@
       </c>
       <c r="I54" s="1"/>
       <c r="J54" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K54" s="1"/>
       <c r="L54" s="1">
@@ -2243,7 +2237,7 @@
       </c>
       <c r="I55" s="1"/>
       <c r="J55" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K55" s="1"/>
       <c r="L55" s="1">
@@ -2275,7 +2269,7 @@
       </c>
       <c r="I56" s="1"/>
       <c r="J56" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K56" s="1"/>
       <c r="L56" s="1">
@@ -2307,7 +2301,7 @@
       </c>
       <c r="I57" s="1"/>
       <c r="J57" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K57" s="1"/>
       <c r="L57" s="1">
@@ -2339,7 +2333,7 @@
       </c>
       <c r="I58" s="1"/>
       <c r="J58" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K58" s="1"/>
       <c r="L58" s="1">
@@ -2371,7 +2365,7 @@
       </c>
       <c r="I59" s="1"/>
       <c r="J59" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K59" s="1"/>
       <c r="L59" s="1">
@@ -2403,7 +2397,7 @@
       </c>
       <c r="I60" s="1"/>
       <c r="J60" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K60" s="1"/>
       <c r="L60" s="1">
@@ -2435,7 +2429,7 @@
       </c>
       <c r="I61" s="1"/>
       <c r="J61" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K61" s="1"/>
       <c r="L61" s="1">
@@ -2467,7 +2461,7 @@
       </c>
       <c r="I62" s="1"/>
       <c r="J62" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K62" s="1"/>
       <c r="L62" s="1">
@@ -2499,7 +2493,7 @@
       </c>
       <c r="I63" s="1"/>
       <c r="J63" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K63" s="1"/>
       <c r="L63" s="1">
@@ -2531,7 +2525,7 @@
       </c>
       <c r="I64" s="1"/>
       <c r="J64" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K64" s="1"/>
       <c r="L64" s="1">
@@ -2563,7 +2557,7 @@
       </c>
       <c r="I65" s="1"/>
       <c r="J65" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K65" s="1"/>
       <c r="L65" s="1">
@@ -2595,7 +2589,7 @@
       </c>
       <c r="I66" s="1"/>
       <c r="J66" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K66" s="1"/>
       <c r="L66" s="1">
@@ -2627,7 +2621,7 @@
       </c>
       <c r="I67" s="1"/>
       <c r="J67" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K67" s="1"/>
       <c r="L67" s="1">
@@ -2659,7 +2653,7 @@
       </c>
       <c r="I68" s="1"/>
       <c r="J68" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K68" s="1"/>
       <c r="L68" s="1">
@@ -2691,7 +2685,7 @@
       </c>
       <c r="I69" s="1"/>
       <c r="J69" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K69" s="1"/>
       <c r="L69" s="1">
@@ -2723,7 +2717,7 @@
       </c>
       <c r="I70" s="1"/>
       <c r="J70" s="1">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="K70" s="1"/>
       <c r="L70" s="1">
@@ -2732,21 +2726,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -2790,13 +2784,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2821,9 +2815,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3860,6 +3854,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -3869,24 +3881,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -1,24 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="22527"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Father\Work\2025_05\ОТЧЕТ ХИМИЧ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCD101A7-2B15-4C28-81E9-35F0E40EA325}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F1EB00-6201-43FB-B91B-60EA4B8B56EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Лист1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029" refMode="R1C1"/>
+  <calcPr calcId="181029" refMode="R1C1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
@@ -173,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -472,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -530,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -561,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -780,23 +786,33 @@
       <c r="D9" s="1">
         <v>45</v>
       </c>
-      <c r="E9" s="1"/>
+      <c r="E9" s="1">
+        <v>33.1</v>
+      </c>
       <c r="F9" s="1">
         <v>35.1</v>
       </c>
-      <c r="G9" s="1"/>
+      <c r="G9" s="1">
+        <v>49.4</v>
+      </c>
       <c r="H9" s="1">
         <v>30</v>
       </c>
-      <c r="I9" s="1"/>
+      <c r="I9" s="1">
+        <v>35.6</v>
+      </c>
       <c r="J9" s="1">
         <v>12</v>
       </c>
-      <c r="K9" s="1"/>
+      <c r="K9" s="1">
+        <v>6</v>
+      </c>
       <c r="L9" s="1">
         <v>13.5</v>
       </c>
-      <c r="M9" s="1"/>
+      <c r="M9" s="1">
+        <v>14.4</v>
+      </c>
     </row>
     <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="2">
@@ -812,23 +828,33 @@
       <c r="D10" s="1">
         <v>45</v>
       </c>
-      <c r="E10" s="1"/>
+      <c r="E10" s="1">
+        <v>34.4</v>
+      </c>
       <c r="F10" s="1">
         <v>35.1</v>
       </c>
-      <c r="G10" s="1"/>
+      <c r="G10" s="1">
+        <v>49.6</v>
+      </c>
       <c r="H10" s="1">
         <v>30</v>
       </c>
-      <c r="I10" s="1"/>
+      <c r="I10" s="1">
+        <v>35.700000000000003</v>
+      </c>
       <c r="J10" s="1">
         <v>12</v>
       </c>
-      <c r="K10" s="1"/>
+      <c r="K10" s="1">
+        <v>6.5</v>
+      </c>
       <c r="L10" s="1">
         <v>13.5</v>
       </c>
-      <c r="M10" s="1"/>
+      <c r="M10" s="1">
+        <v>14.4</v>
+      </c>
     </row>
     <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
@@ -844,23 +870,34 @@
       <c r="D11" s="1">
         <v>45</v>
       </c>
-      <c r="E11" s="1"/>
+      <c r="E11" s="1">
+        <f>86.7</f>
+        <v>86.7</v>
+      </c>
       <c r="F11" s="1">
         <v>35.1</v>
       </c>
-      <c r="G11" s="1"/>
+      <c r="G11" s="1">
+        <v>49.7</v>
+      </c>
       <c r="H11" s="1">
         <v>30</v>
       </c>
-      <c r="I11" s="1"/>
+      <c r="I11" s="1">
+        <v>35.700000000000003</v>
+      </c>
       <c r="J11" s="1">
         <v>12</v>
       </c>
-      <c r="K11" s="1"/>
+      <c r="K11" s="1">
+        <v>6.5</v>
+      </c>
       <c r="L11" s="1">
         <v>13.5</v>
       </c>
-      <c r="M11" s="1"/>
+      <c r="M11" s="1">
+        <v>14.4</v>
+      </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
@@ -1599,21 +1636,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1657,13 +1694,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1688,9 +1725,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -1907,23 +1944,33 @@
       <c r="D45" s="1">
         <v>15</v>
       </c>
-      <c r="E45" s="1"/>
+      <c r="E45" s="1">
+        <v>35</v>
+      </c>
       <c r="F45" s="1">
         <v>10</v>
       </c>
-      <c r="G45" s="1"/>
+      <c r="G45" s="1">
+        <v>6.3</v>
+      </c>
       <c r="H45" s="1">
         <v>7.4</v>
       </c>
-      <c r="I45" s="1"/>
+      <c r="I45" s="1">
+        <v>9</v>
+      </c>
       <c r="J45" s="1">
         <v>5</v>
       </c>
-      <c r="K45" s="1"/>
+      <c r="K45" s="1">
+        <v>4.3</v>
+      </c>
       <c r="L45" s="1">
         <v>2.8</v>
       </c>
-      <c r="M45" s="1"/>
+      <c r="M45" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="2">
@@ -1939,23 +1986,33 @@
       <c r="D46" s="1">
         <v>15</v>
       </c>
-      <c r="E46" s="1"/>
+      <c r="E46" s="1">
+        <v>35.700000000000003</v>
+      </c>
       <c r="F46" s="1">
         <v>10</v>
       </c>
-      <c r="G46" s="1"/>
+      <c r="G46" s="1">
+        <v>6.3</v>
+      </c>
       <c r="H46" s="1">
         <v>7.4</v>
       </c>
-      <c r="I46" s="1"/>
+      <c r="I46" s="1">
+        <v>9</v>
+      </c>
       <c r="J46" s="1">
         <v>5</v>
       </c>
-      <c r="K46" s="1"/>
+      <c r="K46" s="1">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="L46" s="1">
         <v>2.8</v>
       </c>
-      <c r="M46" s="1"/>
+      <c r="M46" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="1">
@@ -1971,23 +2028,34 @@
       <c r="D47" s="1">
         <v>15</v>
       </c>
-      <c r="E47" s="1"/>
+      <c r="E47" s="1">
+        <f>35.7</f>
+        <v>35.700000000000003</v>
+      </c>
       <c r="F47" s="1">
         <v>10</v>
       </c>
-      <c r="G47" s="1"/>
+      <c r="G47" s="1">
+        <v>6.3</v>
+      </c>
       <c r="H47" s="1">
         <v>7.4</v>
       </c>
-      <c r="I47" s="1"/>
+      <c r="I47" s="1">
+        <v>9</v>
+      </c>
       <c r="J47" s="1">
         <v>5</v>
       </c>
-      <c r="K47" s="1"/>
+      <c r="K47" s="1">
+        <v>4.4000000000000004</v>
+      </c>
       <c r="L47" s="1">
         <v>2.8</v>
       </c>
-      <c r="M47" s="1"/>
+      <c r="M47" s="1">
+        <v>5.4</v>
+      </c>
     </row>
     <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="2">
@@ -2726,21 +2794,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -2784,13 +2852,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2815,9 +2883,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3034,23 +3102,33 @@
       <c r="D80" s="1">
         <v>22</v>
       </c>
-      <c r="E80" s="1"/>
+      <c r="E80" s="1">
+        <v>36.1</v>
+      </c>
       <c r="F80" s="1">
         <v>6</v>
       </c>
-      <c r="G80" s="1"/>
+      <c r="G80" s="1">
+        <v>10</v>
+      </c>
       <c r="H80" s="1">
         <v>4.5</v>
       </c>
-      <c r="I80" s="1"/>
+      <c r="I80" s="1">
+        <v>10.6</v>
+      </c>
       <c r="J80" s="1">
         <v>5</v>
       </c>
-      <c r="K80" s="1"/>
+      <c r="K80" s="1">
+        <v>15.4</v>
+      </c>
       <c r="L80" s="1">
         <v>2.7</v>
       </c>
-      <c r="M80" s="1"/>
+      <c r="M80" s="1">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="81" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A81" s="2">
@@ -3066,23 +3144,33 @@
       <c r="D81" s="1">
         <v>22</v>
       </c>
-      <c r="E81" s="1"/>
+      <c r="E81" s="1">
+        <v>36.5</v>
+      </c>
       <c r="F81" s="1">
         <v>6</v>
       </c>
-      <c r="G81" s="1"/>
+      <c r="G81" s="1">
+        <v>10</v>
+      </c>
       <c r="H81" s="1">
         <v>4.5</v>
       </c>
-      <c r="I81" s="1"/>
+      <c r="I81" s="1">
+        <v>10.6</v>
+      </c>
       <c r="J81" s="1">
         <v>5</v>
       </c>
-      <c r="K81" s="1"/>
+      <c r="K81" s="1">
+        <v>15.4</v>
+      </c>
       <c r="L81" s="1">
         <v>2.7</v>
       </c>
-      <c r="M81" s="1"/>
+      <c r="M81" s="1">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="82" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A82" s="1">
@@ -3098,23 +3186,34 @@
       <c r="D82" s="1">
         <v>22</v>
       </c>
-      <c r="E82" s="1"/>
+      <c r="E82" s="1">
+        <f>36.5+1</f>
+        <v>37.5</v>
+      </c>
       <c r="F82" s="1">
         <v>6</v>
       </c>
-      <c r="G82" s="1"/>
+      <c r="G82" s="1">
+        <v>10</v>
+      </c>
       <c r="H82" s="1">
         <v>4.5</v>
       </c>
-      <c r="I82" s="1"/>
+      <c r="I82" s="1">
+        <v>10.6</v>
+      </c>
       <c r="J82" s="1">
         <v>5</v>
       </c>
-      <c r="K82" s="1"/>
+      <c r="K82" s="1">
+        <v>15.4</v>
+      </c>
       <c r="L82" s="1">
         <v>2.7</v>
       </c>
-      <c r="M82" s="1"/>
+      <c r="M82" s="1">
+        <v>6.5</v>
+      </c>
     </row>
     <row r="83" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A83" s="2">
@@ -3854,6 +3953,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -3863,24 +3980,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="C74:C75"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{20F1EB00-6201-43FB-B91B-60EA4B8B56EC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F248F8-7816-4425-8495-686D3DA8414A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -913,23 +913,33 @@
       <c r="D12" s="1">
         <v>45</v>
       </c>
-      <c r="E12" s="1"/>
+      <c r="E12" s="1">
+        <v>74.8</v>
+      </c>
       <c r="F12" s="1">
         <v>35.1</v>
       </c>
-      <c r="G12" s="1"/>
+      <c r="G12" s="1">
+        <v>49.2</v>
+      </c>
       <c r="H12" s="1">
         <v>30</v>
       </c>
-      <c r="I12" s="1"/>
+      <c r="I12" s="1">
+        <v>43.1</v>
+      </c>
       <c r="J12" s="1">
         <v>12</v>
       </c>
-      <c r="K12" s="1"/>
+      <c r="K12" s="1">
+        <v>16</v>
+      </c>
       <c r="L12" s="1">
         <v>13.5</v>
       </c>
-      <c r="M12" s="1"/>
+      <c r="M12" s="1">
+        <v>20.100000000000001</v>
+      </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A13" s="1">
@@ -2071,23 +2081,34 @@
       <c r="D48" s="1">
         <v>15</v>
       </c>
-      <c r="E48" s="1"/>
+      <c r="E48" s="1">
+        <f>44.4</f>
+        <v>44.4</v>
+      </c>
       <c r="F48" s="1">
         <v>10</v>
       </c>
-      <c r="G48" s="1"/>
+      <c r="G48" s="1">
+        <v>20.7</v>
+      </c>
       <c r="H48" s="1">
         <v>7.4</v>
       </c>
-      <c r="I48" s="1"/>
+      <c r="I48" s="1">
+        <v>19.600000000000001</v>
+      </c>
       <c r="J48" s="1">
         <v>5</v>
       </c>
-      <c r="K48" s="1"/>
+      <c r="K48" s="1">
+        <v>3</v>
+      </c>
       <c r="L48" s="1">
         <v>2.8</v>
       </c>
-      <c r="M48" s="1"/>
+      <c r="M48" s="1">
+        <v>10.4</v>
+      </c>
     </row>
     <row r="49" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A49" s="1">
@@ -3229,23 +3250,34 @@
       <c r="D83" s="1">
         <v>22</v>
       </c>
-      <c r="E83" s="1"/>
+      <c r="E83" s="1">
+        <f>28.1</f>
+        <v>28.1</v>
+      </c>
       <c r="F83" s="1">
         <v>6</v>
       </c>
-      <c r="G83" s="1"/>
+      <c r="G83" s="1">
+        <v>9.9</v>
+      </c>
       <c r="H83" s="1">
         <v>4.5</v>
       </c>
-      <c r="I83" s="1"/>
+      <c r="I83" s="1">
+        <v>8.3000000000000007</v>
+      </c>
       <c r="J83" s="1">
         <v>5</v>
       </c>
-      <c r="K83" s="1"/>
+      <c r="K83" s="1">
+        <v>13.7</v>
+      </c>
       <c r="L83" s="1">
         <v>2.7</v>
       </c>
-      <c r="M83" s="1"/>
+      <c r="M83" s="1">
+        <v>6</v>
+      </c>
     </row>
     <row r="84" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A84" s="1">

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01F248F8-7816-4425-8495-686D3DA8414A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4C6B57-331A-4F6F-AE49-CB75F73686F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -955,23 +955,34 @@
       <c r="D13" s="1">
         <v>45</v>
       </c>
-      <c r="E13" s="1"/>
+      <c r="E13" s="1">
+        <f>61.4</f>
+        <v>61.4</v>
+      </c>
       <c r="F13" s="1">
         <v>35.1</v>
       </c>
-      <c r="G13" s="1"/>
+      <c r="G13" s="1">
+        <v>46.7</v>
+      </c>
       <c r="H13" s="1">
         <v>30</v>
       </c>
-      <c r="I13" s="1"/>
+      <c r="I13" s="1">
+        <v>40.4</v>
+      </c>
       <c r="J13" s="1">
         <v>12</v>
       </c>
-      <c r="K13" s="1"/>
+      <c r="K13" s="1">
+        <v>12</v>
+      </c>
       <c r="L13" s="1">
         <v>13.5</v>
       </c>
-      <c r="M13" s="1"/>
+      <c r="M13" s="1">
+        <v>14.5</v>
+      </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A14" s="2">
@@ -1646,21 +1657,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1704,13 +1715,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1735,9 +1746,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2124,23 +2135,34 @@
       <c r="D49" s="1">
         <v>15</v>
       </c>
-      <c r="E49" s="1"/>
+      <c r="E49" s="1">
+        <f>32.5</f>
+        <v>32.5</v>
+      </c>
       <c r="F49" s="1">
         <v>10</v>
       </c>
-      <c r="G49" s="1"/>
+      <c r="G49" s="1">
+        <v>18.2</v>
+      </c>
       <c r="H49" s="1">
         <v>7.4</v>
       </c>
-      <c r="I49" s="1"/>
+      <c r="I49" s="1">
+        <v>17.2</v>
+      </c>
       <c r="J49" s="1">
         <v>5</v>
       </c>
-      <c r="K49" s="1"/>
+      <c r="K49" s="1">
+        <v>9.6</v>
+      </c>
       <c r="L49" s="1">
         <v>2.8</v>
       </c>
-      <c r="M49" s="1"/>
+      <c r="M49" s="1">
+        <v>9.4</v>
+      </c>
     </row>
     <row r="50" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A50" s="2">
@@ -2815,21 +2837,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -2873,13 +2895,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2904,9 +2926,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3293,23 +3315,34 @@
       <c r="D84" s="1">
         <v>22</v>
       </c>
-      <c r="E84" s="1"/>
+      <c r="E84" s="1">
+        <f>18.9+16</f>
+        <v>34.9</v>
+      </c>
       <c r="F84" s="1">
         <v>6</v>
       </c>
-      <c r="G84" s="1"/>
+      <c r="G84" s="1">
+        <v>13.1</v>
+      </c>
       <c r="H84" s="1">
         <v>4.5</v>
       </c>
-      <c r="I84" s="1"/>
+      <c r="I84" s="1">
+        <v>6.2</v>
+      </c>
       <c r="J84" s="1">
         <v>5</v>
       </c>
-      <c r="K84" s="1"/>
+      <c r="K84" s="1">
+        <v>11.9</v>
+      </c>
       <c r="L84" s="1">
         <v>2.7</v>
       </c>
-      <c r="M84" s="1"/>
+      <c r="M84" s="1">
+        <v>4.8</v>
+      </c>
     </row>
     <row r="85" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A85" s="2">
@@ -3985,6 +4018,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -3994,24 +4045,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A4C6B57-331A-4F6F-AE49-CB75F73686F5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A67B7C-F033-4A4E-8413-0E18E050956B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="4" t="s">
+      <c r="A1" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="4"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-      <c r="L1" s="4"/>
-      <c r="M1" s="4"/>
+      <c r="B1" s="5"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
+      <c r="I1" s="5"/>
+      <c r="J1" s="5"/>
+      <c r="K1" s="5"/>
+      <c r="L1" s="5"/>
+      <c r="M1" s="5"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="5"/>
-      <c r="B4" s="5"/>
-      <c r="C4" s="5"/>
+      <c r="A4" s="4"/>
+      <c r="B4" s="4"/>
+      <c r="C4" s="4"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -998,23 +998,34 @@
       <c r="D14" s="1">
         <v>45</v>
       </c>
-      <c r="E14" s="1"/>
+      <c r="E14" s="1">
+        <f>37.3</f>
+        <v>37.299999999999997</v>
+      </c>
       <c r="F14" s="1">
         <v>35.1</v>
       </c>
-      <c r="G14" s="1"/>
+      <c r="G14" s="1">
+        <v>54.9</v>
+      </c>
       <c r="H14" s="1">
         <v>30</v>
       </c>
-      <c r="I14" s="1"/>
+      <c r="I14" s="1">
+        <v>33.799999999999997</v>
+      </c>
       <c r="J14" s="1">
         <v>12</v>
       </c>
-      <c r="K14" s="1"/>
+      <c r="K14" s="1">
+        <v>9.9</v>
+      </c>
       <c r="L14" s="1">
         <v>13.5</v>
       </c>
-      <c r="M14" s="1"/>
+      <c r="M14" s="1">
+        <v>10.9</v>
+      </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A15" s="1">
@@ -1657,21 +1668,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="4" t="s">
+      <c r="A37" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="4"/>
-      <c r="C37" s="4"/>
-      <c r="D37" s="4"/>
-      <c r="E37" s="4"/>
-      <c r="F37" s="4"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="4"/>
-      <c r="I37" s="4"/>
-      <c r="J37" s="4"/>
-      <c r="K37" s="4"/>
-      <c r="L37" s="4"/>
-      <c r="M37" s="4"/>
+      <c r="B37" s="5"/>
+      <c r="C37" s="5"/>
+      <c r="D37" s="5"/>
+      <c r="E37" s="5"/>
+      <c r="F37" s="5"/>
+      <c r="G37" s="5"/>
+      <c r="H37" s="5"/>
+      <c r="I37" s="5"/>
+      <c r="J37" s="5"/>
+      <c r="K37" s="5"/>
+      <c r="L37" s="5"/>
+      <c r="M37" s="5"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1715,13 +1726,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="5" t="s">
+      <c r="B39" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="5" t="s">
+      <c r="C39" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1746,9 +1757,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="5"/>
-      <c r="B40" s="5"/>
-      <c r="C40" s="5"/>
+      <c r="A40" s="4"/>
+      <c r="B40" s="4"/>
+      <c r="C40" s="4"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2178,23 +2189,34 @@
       <c r="D50" s="1">
         <v>15</v>
       </c>
-      <c r="E50" s="1"/>
+      <c r="E50" s="1">
+        <f>21.8+16.7</f>
+        <v>38.5</v>
+      </c>
       <c r="F50" s="1">
         <v>10</v>
       </c>
-      <c r="G50" s="1"/>
+      <c r="G50" s="1">
+        <v>16.100000000000001</v>
+      </c>
       <c r="H50" s="1">
         <v>7.4</v>
       </c>
-      <c r="I50" s="1"/>
+      <c r="I50" s="1">
+        <v>15.2</v>
+      </c>
       <c r="J50" s="1">
         <v>5</v>
       </c>
-      <c r="K50" s="1"/>
+      <c r="K50" s="1">
+        <v>8.5</v>
+      </c>
       <c r="L50" s="1">
         <v>2.8</v>
       </c>
-      <c r="M50" s="1"/>
+      <c r="M50" s="1">
+        <v>8.6</v>
+      </c>
     </row>
     <row r="51" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A51" s="1">
@@ -2837,21 +2859,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="4" t="s">
+      <c r="A72" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="4"/>
-      <c r="C72" s="4"/>
-      <c r="D72" s="4"/>
-      <c r="E72" s="4"/>
-      <c r="F72" s="4"/>
-      <c r="G72" s="4"/>
-      <c r="H72" s="4"/>
-      <c r="I72" s="4"/>
-      <c r="J72" s="4"/>
-      <c r="K72" s="4"/>
-      <c r="L72" s="4"/>
-      <c r="M72" s="4"/>
+      <c r="B72" s="5"/>
+      <c r="C72" s="5"/>
+      <c r="D72" s="5"/>
+      <c r="E72" s="5"/>
+      <c r="F72" s="5"/>
+      <c r="G72" s="5"/>
+      <c r="H72" s="5"/>
+      <c r="I72" s="5"/>
+      <c r="J72" s="5"/>
+      <c r="K72" s="5"/>
+      <c r="L72" s="5"/>
+      <c r="M72" s="5"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -2895,13 +2917,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="5" t="s">
+      <c r="A74" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="5" t="s">
+      <c r="C74" s="4" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2926,9 +2948,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="5"/>
-      <c r="B75" s="5"/>
-      <c r="C75" s="5"/>
+      <c r="A75" s="4"/>
+      <c r="B75" s="4"/>
+      <c r="C75" s="4"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3358,23 +3380,34 @@
       <c r="D85" s="1">
         <v>22</v>
       </c>
-      <c r="E85" s="1"/>
+      <c r="E85" s="1">
+        <f>25.1+3</f>
+        <v>28.1</v>
+      </c>
       <c r="F85" s="1">
         <v>6</v>
       </c>
-      <c r="G85" s="1"/>
+      <c r="G85" s="1">
+        <v>10.3</v>
+      </c>
       <c r="H85" s="1">
         <v>4.5</v>
       </c>
-      <c r="I85" s="1"/>
+      <c r="I85" s="1">
+        <v>11</v>
+      </c>
       <c r="J85" s="1">
         <v>5</v>
       </c>
-      <c r="K85" s="1"/>
+      <c r="K85" s="1">
+        <v>10.3</v>
+      </c>
       <c r="L85" s="1">
         <v>2.7</v>
       </c>
-      <c r="M85" s="1"/>
+      <c r="M85" s="1">
+        <v>8.9</v>
+      </c>
     </row>
     <row r="86" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A86" s="1">
@@ -4018,6 +4051,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A72:M72"/>
+    <mergeCell ref="A74:A75"/>
+    <mergeCell ref="B74:B75"/>
+    <mergeCell ref="D74:E74"/>
+    <mergeCell ref="F74:G74"/>
+    <mergeCell ref="H74:I74"/>
+    <mergeCell ref="J74:K74"/>
+    <mergeCell ref="L74:M74"/>
+    <mergeCell ref="C74:C75"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A3:A4"/>
     <mergeCell ref="A1:M1"/>
     <mergeCell ref="D3:E3"/>
@@ -4027,24 +4078,6 @@
     <mergeCell ref="L3:M3"/>
     <mergeCell ref="B3:B4"/>
     <mergeCell ref="C3:C4"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A72:M72"/>
-    <mergeCell ref="A74:A75"/>
-    <mergeCell ref="B74:B75"/>
-    <mergeCell ref="D74:E74"/>
-    <mergeCell ref="F74:G74"/>
-    <mergeCell ref="H74:I74"/>
-    <mergeCell ref="J74:K74"/>
-    <mergeCell ref="L74:M74"/>
-    <mergeCell ref="C74:C75"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
+++ b/ОТЧЕТ ХИМИЧ/Остатки на Складах КИ ПОКОМ ПЛАН.ФАКТ(09,26).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\ОТЧЕТ ХИМИЧ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E7A67B7C-F033-4A4E-8413-0E18E050956B}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{171D180F-611A-4723-8786-FD02F2120A90}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -179,11 +179,11 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -478,21 +478,21 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="5"/>
-      <c r="C1" s="5"/>
-      <c r="D1" s="5"/>
-      <c r="E1" s="5"/>
-      <c r="F1" s="5"/>
-      <c r="G1" s="5"/>
-      <c r="H1" s="5"/>
-      <c r="I1" s="5"/>
-      <c r="J1" s="5"/>
-      <c r="K1" s="5"/>
-      <c r="L1" s="5"/>
-      <c r="M1" s="5"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="4"/>
+      <c r="D1" s="4"/>
+      <c r="E1" s="4"/>
+      <c r="F1" s="4"/>
+      <c r="G1" s="4"/>
+      <c r="H1" s="4"/>
+      <c r="I1" s="4"/>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+      <c r="L1" s="4"/>
+      <c r="M1" s="4"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
@@ -536,13 +536,13 @@
       </c>
     </row>
     <row r="3" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+      <c r="A3" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D3" s="6" t="s">
@@ -567,9 +567,9 @@
       <c r="M3" s="6"/>
     </row>
     <row r="4" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A4" s="4"/>
-      <c r="B4" s="4"/>
-      <c r="C4" s="4"/>
+      <c r="A4" s="5"/>
+      <c r="B4" s="5"/>
+      <c r="C4" s="5"/>
       <c r="D4" s="1" t="s">
         <v>1</v>
       </c>
@@ -1041,23 +1041,34 @@
       <c r="D15" s="1">
         <v>45</v>
       </c>
-      <c r="E15" s="1"/>
+      <c r="E15" s="1">
+        <f>37.4</f>
+        <v>37.4</v>
+      </c>
       <c r="F15" s="1">
         <v>35.1</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1">
+        <v>56.2</v>
+      </c>
       <c r="H15" s="1">
         <v>30</v>
       </c>
-      <c r="I15" s="1"/>
+      <c r="I15" s="1">
+        <v>25.9</v>
+      </c>
       <c r="J15" s="1">
         <v>12</v>
       </c>
-      <c r="K15" s="1"/>
+      <c r="K15" s="1">
+        <v>8.1</v>
+      </c>
       <c r="L15" s="1">
         <v>13.5</v>
       </c>
-      <c r="M15" s="1"/>
+      <c r="M15" s="1">
+        <v>8.1</v>
+      </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A16" s="2">
@@ -1668,21 +1679,21 @@
       <c r="M34" s="1"/>
     </row>
     <row r="37" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="B37" s="5"/>
-      <c r="C37" s="5"/>
-      <c r="D37" s="5"/>
-      <c r="E37" s="5"/>
-      <c r="F37" s="5"/>
-      <c r="G37" s="5"/>
-      <c r="H37" s="5"/>
-      <c r="I37" s="5"/>
-      <c r="J37" s="5"/>
-      <c r="K37" s="5"/>
-      <c r="L37" s="5"/>
-      <c r="M37" s="5"/>
+      <c r="B37" s="4"/>
+      <c r="C37" s="4"/>
+      <c r="D37" s="4"/>
+      <c r="E37" s="4"/>
+      <c r="F37" s="4"/>
+      <c r="G37" s="4"/>
+      <c r="H37" s="4"/>
+      <c r="I37" s="4"/>
+      <c r="J37" s="4"/>
+      <c r="K37" s="4"/>
+      <c r="L37" s="4"/>
+      <c r="M37" s="4"/>
     </row>
     <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="1">
@@ -1726,13 +1737,13 @@
       </c>
     </row>
     <row r="39" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A39" s="4" t="s">
+      <c r="A39" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B39" s="4" t="s">
+      <c r="B39" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C39" s="4" t="s">
+      <c r="C39" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D39" s="6" t="s">
@@ -1757,9 +1768,9 @@
       <c r="M39" s="6"/>
     </row>
     <row r="40" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A40" s="4"/>
-      <c r="B40" s="4"/>
-      <c r="C40" s="4"/>
+      <c r="A40" s="5"/>
+      <c r="B40" s="5"/>
+      <c r="C40" s="5"/>
       <c r="D40" s="1" t="s">
         <v>1</v>
       </c>
@@ -2232,23 +2243,34 @@
       <c r="D51" s="1">
         <v>15</v>
       </c>
-      <c r="E51" s="1"/>
+      <c r="E51" s="1">
+        <f>30.6</f>
+        <v>30.6</v>
+      </c>
       <c r="F51" s="1">
         <v>10</v>
       </c>
-      <c r="G51" s="1"/>
+      <c r="G51" s="1">
+        <v>14.3</v>
+      </c>
       <c r="H51" s="1">
         <v>7.4</v>
       </c>
-      <c r="I51" s="1"/>
+      <c r="I51" s="1">
+        <v>13.1</v>
+      </c>
       <c r="J51" s="1">
         <v>5</v>
       </c>
-      <c r="K51" s="1"/>
+      <c r="K51" s="1">
+        <v>7.7</v>
+      </c>
       <c r="L51" s="1">
         <v>2.8</v>
       </c>
-      <c r="M51" s="1"/>
+      <c r="M51" s="1">
+        <v>8.1999999999999993</v>
+      </c>
     </row>
     <row r="52" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A52" s="2">
@@ -2859,21 +2881,21 @@
       <c r="M70" s="1"/>
     </row>
     <row r="72" spans="1:13" ht="21" x14ac:dyDescent="0.35">
-      <c r="A72" s="5" t="s">
+      <c r="A72" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B72" s="5"/>
-      <c r="C72" s="5"/>
-      <c r="D72" s="5"/>
-      <c r="E72" s="5"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
-      <c r="H72" s="5"/>
-      <c r="I72" s="5"/>
-      <c r="J72" s="5"/>
-      <c r="K72" s="5"/>
-      <c r="L72" s="5"/>
-      <c r="M72" s="5"/>
+      <c r="B72" s="4"/>
+      <c r="C72" s="4"/>
+      <c r="D72" s="4"/>
+      <c r="E72" s="4"/>
+      <c r="F72" s="4"/>
+      <c r="G72" s="4"/>
+      <c r="H72" s="4"/>
+      <c r="I72" s="4"/>
+      <c r="J72" s="4"/>
+      <c r="K72" s="4"/>
+      <c r="L72" s="4"/>
+      <c r="M72" s="4"/>
     </row>
     <row r="73" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A73" s="1">
@@ -2917,13 +2939,13 @@
       </c>
     </row>
     <row r="74" spans="1:13" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A74" s="4" t="s">
+      <c r="A74" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B74" s="4" t="s">
+      <c r="B74" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C74" s="4" t="s">
+      <c r="C74" s="5" t="s">
         <v>19</v>
       </c>
       <c r="D74" s="6" t="s">
@@ -2948,9 +2970,9 @@
       <c r="M74" s="6"/>
     </row>
     <row r="75" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A75" s="4"/>
-      <c r="B75" s="4"/>
-      <c r="C75" s="4"/>
+      <c r="A75" s="5"/>
+      <c r="B75" s="5"/>
+      <c r="C75" s="5"/>
       <c r="D75" s="1" t="s">
         <v>1</v>
       </c>
@@ -3423,23 +3445,34 @@
       <c r="D86" s="1">
         <v>22</v>
       </c>
-      <c r="E86" s="1"/>
+      <c r="E86" s="1">
+        <f>19.4+2+12</f>
+        <v>33.4</v>
+      </c>
       <c r="F86" s="1">
         <v>6</v>
       </c>
-      <c r="G86" s="1"/>
+      <c r="G86" s="1">
+        <v>13</v>
+      </c>
       <c r="H86" s="1">
         <v>4.5</v>
       </c>
-      <c r="I86" s="1"/>
+      <c r="I86" s="1">
+        <v>9.1</v>
+      </c>
       <c r="J86" s="1">
         <v>5</v>
       </c>
-      <c r="K86" s="1"/>
+      <c r="K86" s="1">
+        <v>9.8000000000000007</v>
+      </c>
       <c r="L86" s="1">
         <v>2.7</v>
       </c>
-      <c r="M86" s="1"/>
+      <c r="M86" s="1">
+        <v>8</v>
+      </c>
     </row>
     <row r="87" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A87" s="2">
@@ -4051,6 +4084,24 @@
     </row>
   </sheetData>
   <mergeCells count="27">
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A1:M1"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="B3:B4"/>
+    <mergeCell ref="C3:C4"/>
+    <mergeCell ref="A37:M37"/>
+    <mergeCell ref="A39:A40"/>
+    <mergeCell ref="B39:B40"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="C39:C40"/>
     <mergeCell ref="A72:M72"/>
     <mergeCell ref="A74:A75"/>
     <mergeCell ref="B74:B75"/>
@@ -4060,24 +4111,6 @@
     <mergeCell ref="J74:K74"/>
     <mergeCell ref="L74:M74"/>
     <mergeCell ref="C74:C75"/>
-    <mergeCell ref="A37:M37"/>
-    <mergeCell ref="A39:A40"/>
-    <mergeCell ref="B39:B40"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="C39:C40"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A1:M1"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
-    <mergeCell ref="B3:B4"/>
-    <mergeCell ref="C3:C4"/>
   </mergeCells>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
